--- a/backend/tasks.xlsx
+++ b/backend/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\projects\online-training\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BE55BB-8BB6-4900-98A4-4297E281FC41}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3E1974-9CD9-4CDF-99DE-CB2C19C121D6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{8A61F1D3-1E5C-42D8-B77F-2D570F6A0CD9}"/>
   </bookViews>
@@ -177,9 +177,6 @@
     <t>Четырехугольник $ABCD$ вписан в окружность. Угол $ABC$ равен 105°, угол $CAD$ равен 35°. Найдите угол $ABD$. Ответ дайте в градусах.</t>
   </si>
   <si>
-    <t>Даны точки $A(1, 3)$ и $B(5, 7)$. Найдите длину вектора $\vec{AB}$.</t>
-  </si>
-  <si>
     <t>Найдите косинус угла между векторами $\vec{a}(2, 3)$ и $\vec{b}(-1, 4)$.</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>Радиус основания цилиндра равен 3, высота равна 5. Найдите площадь полной поверхности цилиндра, деленную на $\pi$.</t>
+  </si>
+  <si>
+    <t>Даны точки $A(1, 4)$ и $B(5, 7)$. Найдите длину вектора $\vec{AB}$.</t>
   </si>
 </sst>
 </file>
@@ -1289,10 +1289,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1306,7 +1306,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>33</v>
@@ -1323,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1">
         <v>8</v>
@@ -1340,7 +1340,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1">
         <v>72</v>
@@ -1374,7 +1374,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1">
         <v>48</v>
